--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/mtann 20260424084349.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/mtann 20260424084349.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157E7404-9167-4A59-98F8-1C67FFA227E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED71D66-0792-E043-8C42-7CD83393FF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8508" yWindow="0" windowWidth="14628" windowHeight="12336" xr2:uid="{33FD0A33-76C2-402A-B742-045D1BF053F3}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="12820" xr2:uid="{33FD0A33-76C2-402A-B742-045D1BF053F3}"/>
   </bookViews>
   <sheets>
     <sheet name="mtann 20260424084349" sheetId="1" r:id="rId1"/>
@@ -58,10 +58,10 @@
     <t>2026-04-24 18:54:42 EDT</t>
   </si>
   <si>
-    <t>/img_Windows_Ransomware_Build.vmdk/vol_vol6/Users/mtann/lol.txt</t>
-  </si>
-  <si>
     <t>txt</t>
+  </si>
+  <si>
+    <t>~/Users/mtann/lol.txt</t>
   </si>
 </sst>
 </file>
@@ -603,6 +603,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5781228E-C464-1945-A37E-2BB4B2D17DB0}" name="Table1" displayName="Table1" ref="A1:H2" totalsRowShown="0">
+  <autoFilter ref="A1:H2" xr:uid="{5781228E-C464-1945-A37E-2BB4B2D17DB0}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{81E317F7-C993-784E-A9D6-14CB3FD9F8DF}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{EF6547D8-758E-584C-95EF-CA6278F45CB4}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{B06B7FA2-5D89-7B41-A5FF-C79959211EF5}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{575ECF80-77EE-974C-9B09-39D5BF4975E0}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{6584AF8D-8000-7244-8EA1-417773F25D57}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{C6A7D3D5-5747-D945-AC25-018BB7DE5840}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{910753C9-9D75-6440-9F92-D610A40BC9A1}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{25130BB7-0814-3E44-9D3A-498D5F7BC82E}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -923,16 +940,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3262E1D-B929-4DD9-88AC-751E882B925A}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -978,13 +995,16 @@
         <v>332</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>